--- a/backend/data/frameworks/excel/AI Audit Agent - Evaluation Framework.xlsx
+++ b/backend/data/frameworks/excel/AI Audit Agent - Evaluation Framework.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://procdna-my.sharepoint.com/personal/avishi_jain_procdna_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI Audit Platform\backend\data\frameworks\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{9B8C1AA1-E12F-4E34-BB61-963D52C1116E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34C76120-6CE4-40A1-BFFF-4A65E2D6624D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693FC0D3-9D97-48E1-AC11-34358AFA26EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{397319AA-9A4C-4BE1-B71D-AE2DAE7876CD}"/>
   </bookViews>
   <sheets>
     <sheet name="STAR Evaluation Framework" sheetId="2" r:id="rId1"/>
-    <sheet name="DEx Evaluation Framework" sheetId="3" r:id="rId2"/>
+    <sheet name="DEx Evaluation Framework" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DEx Evaluation Framework'!$A$1:$E$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STAR Evaluation Framework'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="844">
   <si>
     <t>Document</t>
   </si>
@@ -58,9 +57,6 @@
     <t>Evaluation Pointers</t>
   </si>
   <si>
-    <t>Functional Requirement Document</t>
-  </si>
-  <si>
     <t>Must Have</t>
   </si>
   <si>
@@ -325,13 +321,6 @@
     <t>Test Case Coverage</t>
   </si>
   <si>
-    <t>Verify whether all relevant test cases of data validation, UI/UX, functional, security and access testing.
-Reporting/Dashboarding project: KPIs, reports, dashboards, charts, filters, modules etc. are covered in SIT scenarios
-Datawarehouse project: Medallion layer wise tables, column business rules, aggregated layers vs source layers, reporting and/or analytical layer vs source, data standardization &amp; data type checks, Constraint checks, specific use case if part of requirements
-Report/Dashboard to Datawarehouse project: Frontend backend value match
-Custom App: UI/UX, Functionality, Frontend to Backend Data Validation</t>
-  </si>
-  <si>
     <t>Module-wise Test Categorization</t>
   </si>
   <si>
@@ -480,13 +469,2119 @@
   </si>
   <si>
     <t>Project Initiation</t>
+  </si>
+  <si>
+    <t>Requirement Traceability</t>
+  </si>
+  <si>
+    <t>Verify whether each specification points back to the business or functional requirement it satisfies</t>
+  </si>
+  <si>
+    <t>System Behaviour Defined</t>
+  </si>
+  <si>
+    <t>Verify whether the document says what the system does when a user takes an action</t>
+  </si>
+  <si>
+    <t>Field-level Specification</t>
+  </si>
+  <si>
+    <t>Verify whether inputs and outputs are named at field level with types, formats and mandatory flags</t>
+  </si>
+  <si>
+    <t>Calculation Logic</t>
+  </si>
+  <si>
+    <t>Verify whether every calculation and derivation is written out precisely enough that two developers would build it identically</t>
+  </si>
+  <si>
+    <t>Volume &amp; Retention</t>
+  </si>
+  <si>
+    <t>Verify whether expected volumes, the historical load period and retention requirements are stated</t>
+  </si>
+  <si>
+    <t>Process Flow</t>
+  </si>
+  <si>
+    <t>Verify whether end-to-end process flows are documented with their sequence and decision branches</t>
+  </si>
+  <si>
+    <t>Edge Case Coverage</t>
+  </si>
+  <si>
+    <t>Check whether nulls, boundary conditions and negative scenarios are described</t>
+  </si>
+  <si>
+    <t>Verify whether all relevant test cases are covered across data validation, UI/UX, functional, security and access testing, with scenarios matched to the project type: for reporting or dashboarding projects, KPIs, reports, dashboards, charts, filters and modules; for data warehouse projects, medallion layer-wise tables, column business rules, aggregated versus source layers, reporting or analytical layer versus source, data standardisation and data type checks, constraint checks and any use case specific to the requirements; for report or dashboard to data warehouse projects, frontend to backend value match; for custom applications, UI/UX, functionality and frontend to backend data validation</t>
+  </si>
+  <si>
+    <t>Universal Document Standards (Applies to All Documents)</t>
+  </si>
+  <si>
+    <t>All Phases</t>
+  </si>
+  <si>
+    <t>Standard Template Usage</t>
+  </si>
+  <si>
+    <t>Verify whether the document sits on the current ProcDNA template rather than a format someone built themselves</t>
+  </si>
+  <si>
+    <t>File Naming Compliance</t>
+  </si>
+  <si>
+    <t>Verify whether the file name carries the date, project, document title, version and author initials</t>
+  </si>
+  <si>
+    <t>Author &amp; Approver Named</t>
+  </si>
+  <si>
+    <t>Verify whether the document names who wrote it, who reviewed it and who approved it</t>
+  </si>
+  <si>
+    <t>Single Live Version</t>
+  </si>
+  <si>
+    <t>Verify whether only one live copy sits in the working folder, with superseded versions moved to archive</t>
+  </si>
+  <si>
+    <t>Terminology Consistency</t>
+  </si>
+  <si>
+    <t>Verify whether the same thing is called the same name throughout, with terms defined where they first appear</t>
+  </si>
+  <si>
+    <t>e.g. Refer to HCP as either HCP, doctor, MD, prescriber or physician throughout all the documents.</t>
+  </si>
+  <si>
+    <t>Client Repository Sync</t>
+  </si>
+  <si>
+    <t>Check whether documents owed to the client also sit in the client folder and match the internal copy</t>
+  </si>
+  <si>
+    <t>Access &amp; Confidentiality</t>
+  </si>
+  <si>
+    <t>Check whether access is restricted to the right people and any sensitivity marking is applied</t>
+  </si>
+  <si>
+    <t>Evidence Attached</t>
+  </si>
+  <si>
+    <t>Check whether claims of completion are backed by evidence such as screenshots, logs or query output</t>
+  </si>
+  <si>
+    <t>Project Charter / Project Plan / Schedule / Scope</t>
+  </si>
+  <si>
+    <t>Business Case &amp; Objectives</t>
+  </si>
+  <si>
+    <t>Verify whether the charter states the business problem being solved and what success looks like in measurable terms</t>
+  </si>
+  <si>
+    <t>Scope Boundaries</t>
+  </si>
+  <si>
+    <t>Verify whether the charter says what is in scope and, just as plainly, what is not</t>
+  </si>
+  <si>
+    <t>Deliverables &amp; Milestones</t>
+  </si>
+  <si>
+    <t>Verify whether the main deliverables are listed with phase milestones, client review points, approval gates and target dates</t>
+  </si>
+  <si>
+    <t>Sponsor &amp; Governance Structure</t>
+  </si>
+  <si>
+    <t>Verify whether the sponsor, key stakeholders and the forum that makes decisions are all named</t>
+  </si>
+  <si>
+    <t>Team Structure &amp; Allocation</t>
+  </si>
+  <si>
+    <t>Verify whether the charter names the team, their roles and how much of their time the project gets</t>
+  </si>
+  <si>
+    <t>Budget &amp; Effort Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify whether the charter carries a budget and effort estimate </t>
+  </si>
+  <si>
+    <t>Risks &amp; Assumptions</t>
+  </si>
+  <si>
+    <t>Verify whether the known risks, assumptions and constraints are written down with an owner against each</t>
+  </si>
+  <si>
+    <t>Success Criteria</t>
+  </si>
+  <si>
+    <t>Verify whether the charter defines measurable success criteria and how the project will be accepted as complete</t>
+  </si>
+  <si>
+    <t>Delivery Methodology</t>
+  </si>
+  <si>
+    <t>Verify whether the charter states the delivery methodology and the working rhythm that goes with it</t>
+  </si>
+  <si>
+    <t>SOW Alignment</t>
+  </si>
+  <si>
+    <t>Verify whether the charter's scope, timeline and deliverables match what the SOW actually commits to</t>
+  </si>
+  <si>
+    <t>Charter Authorization</t>
+  </si>
+  <si>
+    <t>Verify whether someone with the authority to start the project has signed the charter, with a date</t>
+  </si>
+  <si>
+    <t>Task-level Breakdown</t>
+  </si>
+  <si>
+    <t>Verify whether the work is broken into tasks small enough to track meaningfully</t>
+  </si>
+  <si>
+    <t>Approved Baseline</t>
+  </si>
+  <si>
+    <t>Verify whether an approved baseline exists as the reference against which slippage is measured</t>
+  </si>
+  <si>
+    <t>Task Ownership</t>
+  </si>
+  <si>
+    <t>Verify whether each task names an individual rather than a team</t>
+  </si>
+  <si>
+    <t>Dependencies &amp; Critical Path</t>
+  </si>
+  <si>
+    <t>Verify whether task dependencies, sequencing and the critical path are identified</t>
+  </si>
+  <si>
+    <t>Plan vs Actual</t>
+  </si>
+  <si>
+    <t>Verify whether actual progress is tracked against baseline so variance and slippage are visible</t>
+  </si>
+  <si>
+    <t>Buffer &amp; Timeline Realism</t>
+  </si>
+  <si>
+    <t>Verify whether the plan leaves room for review cycles and defect fixing rather than assuming everything lands first time</t>
+  </si>
+  <si>
+    <t>Solution Approach</t>
+  </si>
+  <si>
+    <t>Check whether the charter outlines how the solution will be built and on what platform</t>
+  </si>
+  <si>
+    <t>Reporting Cadence</t>
+  </si>
+  <si>
+    <t>Check whether the charter sets out reporting cadence, governance meetings and how issues escalate</t>
+  </si>
+  <si>
+    <t>Leave &amp; Holiday Overlay</t>
+  </si>
+  <si>
+    <t>Check whether team leave and holiday calendars are reflected in the schedule</t>
+  </si>
+  <si>
+    <t>RAID Log (Risks, Assumptions, Issues, Dependencies)</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>Full RAID Coverage</t>
+  </si>
+  <si>
+    <t>Verify whether risks, assumptions, issues and dependencies are all present and sitting in the right category</t>
+  </si>
+  <si>
+    <t>Entry ID &amp; Description</t>
+  </si>
+  <si>
+    <t>Verify whether each entry has an ID and a description specific enough to act on</t>
+  </si>
+  <si>
+    <t>Impact &amp; Priority Rating</t>
+  </si>
+  <si>
+    <t>Verify whether each risk carries an impact rating and the priority that follows from them</t>
+  </si>
+  <si>
+    <t>Mitigation &amp; Contingency</t>
+  </si>
+  <si>
+    <t>Verify whether each risk has both a mitigation to stop it happening and a contingency for if it does</t>
+  </si>
+  <si>
+    <t>One Named Owner per Item</t>
+  </si>
+  <si>
+    <t>Verify whether every item names one person as owner rather than a team</t>
+  </si>
+  <si>
+    <t>Dates &amp; Status</t>
+  </si>
+  <si>
+    <t>Verify whether raised date, due date, current status are all maintained</t>
+  </si>
+  <si>
+    <t>Issue Escalation Path</t>
+  </si>
+  <si>
+    <t>Verify whether open issues show an escalation trigger, a contact and the action being taken</t>
+  </si>
+  <si>
+    <t>Dependency Impact</t>
+  </si>
+  <si>
+    <t>Verify whether dependencies name the party being waited on and the timeline impact if they slip</t>
+  </si>
+  <si>
+    <t>Log Currency</t>
+  </si>
+  <si>
+    <t>Verify whether the log is genuinely live, with no items sitting long past their due date</t>
+  </si>
+  <si>
+    <t>Workstream Tagging</t>
+  </si>
+  <si>
+    <t>Check whether items are tagged by workstream or phase so they can be filtered and reported</t>
+  </si>
+  <si>
+    <t>Kick off Deck</t>
+  </si>
+  <si>
+    <t>Project Overview &amp; Objectives</t>
+  </si>
+  <si>
+    <t>Verify whether the deck sets out the project purpose, objectives and expected outcomes for the audience</t>
+  </si>
+  <si>
+    <t>Scope Walkthrough</t>
+  </si>
+  <si>
+    <t>Verify whether in-scope and out-of-scope items were presented so both sides leave with the same understanding</t>
+  </si>
+  <si>
+    <t>Delivery Approach &amp; Timeline</t>
+  </si>
+  <si>
+    <t>Verify whether the delivery methodology, phases, milestones and key dates were presented</t>
+  </si>
+  <si>
+    <t>Team Introductions &amp; Contacts</t>
+  </si>
+  <si>
+    <t>Verify whether delivery and client team members are introduced with names, roles and contact points</t>
+  </si>
+  <si>
+    <t>Tools, Access &amp; Environments</t>
+  </si>
+  <si>
+    <t>Verify whether the tools, repositories and access the project will use are covered, along with who arranges what</t>
+  </si>
+  <si>
+    <t>Assumptions, Risks &amp; Dependencies Raised</t>
+  </si>
+  <si>
+    <t>Verify whether known assumptions, early risks and client-side dependencies were flagged at kick-off</t>
+  </si>
+  <si>
+    <t>Deck Circulated &amp; Acknowledged</t>
+  </si>
+  <si>
+    <t>Verify whether the deck was shared after the session and acknowledged by the client</t>
+  </si>
+  <si>
+    <t>Activity Coverage</t>
+  </si>
+  <si>
+    <t>Verify whether activities are listed at a level granular enough for someone to be held to them</t>
+  </si>
+  <si>
+    <t>Role Definitions &amp; Legend</t>
+  </si>
+  <si>
+    <t>Verify whether roles are spelled out with a RACI legend and real names attached where possible</t>
+  </si>
+  <si>
+    <t>RACI like component</t>
+  </si>
+  <si>
+    <t>Define dependencies, owners, POCs to assign RACI for both Business team from the client side, IT Team from the client side, ProcDNA team/s and/or other vendors</t>
+  </si>
+  <si>
+    <t>Function-wise Coverage</t>
+  </si>
+  <si>
+    <t>Verify whether the RACI covers every function including data, engineering, BI, QA, infrastructure and security</t>
+  </si>
+  <si>
+    <t>Internal Role Definition</t>
+  </si>
+  <si>
+    <t>Verify whether internal roles, reporting lines and individual ownership are defined</t>
+  </si>
+  <si>
+    <t>Handoff Ownership</t>
+  </si>
+  <si>
+    <t>Verify whether each handoff says who passes the work, who receives it and who accepts it</t>
+  </si>
+  <si>
+    <t>Decision Rights</t>
+  </si>
+  <si>
+    <t>Verify whether decision rights for scope, design and release decisions are assigned to named roles</t>
+  </si>
+  <si>
+    <t>Escalation Matrix</t>
+  </si>
+  <si>
+    <t>Verify whether escalation levels, contacts and expected response times are documented</t>
+  </si>
+  <si>
+    <t>Engagement Model</t>
+  </si>
+  <si>
+    <t>Verify whether recurring communication is listed with the purpose it serves with audience, frequency and channel</t>
+  </si>
+  <si>
+    <t>Governance Forums</t>
+  </si>
+  <si>
+    <t>Verify whether status reporting and the governance or steering forums are defined with their cadence</t>
+  </si>
+  <si>
+    <t>Ways of Working</t>
+  </si>
+  <si>
+    <t>Check whether working hours, response expectations and the definition of done are covered</t>
+  </si>
+  <si>
+    <t>Check whether the agreed success criteria are restated so the team starts aligned</t>
+  </si>
+  <si>
+    <t>Next Steps &amp; Immediate Actions</t>
+  </si>
+  <si>
+    <t>Check whether the deck closes with immediate next steps carrying owners and dates</t>
+  </si>
+  <si>
+    <t>Phase-wise Grouping</t>
+  </si>
+  <si>
+    <t>Check whether activities are grouped by phase or workstream so the matrix can be read easily</t>
+  </si>
+  <si>
+    <t>Client Turnaround Times</t>
+  </si>
+  <si>
+    <t>Check whether client-side dependencies such as access, data and approvals carry agreed turnaround times</t>
+  </si>
+  <si>
+    <t>Backup Owners</t>
+  </si>
+  <si>
+    <t>Check whether critical roles have a named backup so absence does not stop the work</t>
+  </si>
+  <si>
+    <t>Overlap Hours</t>
+  </si>
+  <si>
+    <t>Check whether working hours, overlap windows and availability across geographies are addressed</t>
+  </si>
+  <si>
+    <t>Meeting Ground Rules</t>
+  </si>
+  <si>
+    <t>Check whether ground rules on agendas, meeting notes and documentation are set out</t>
+  </si>
+  <si>
+    <t>Plan Kept Current</t>
+  </si>
+  <si>
+    <t>Check whether the plan is refreshed when stakeholders or the meeting rhythm change</t>
+  </si>
+  <si>
+    <t>Change Control Register/Change Tracker</t>
+  </si>
+  <si>
+    <t>CR Identification</t>
+  </si>
+  <si>
+    <t>Verify whether each change carries an ID, who raised it, when, and a description that explains the business reason</t>
+  </si>
+  <si>
+    <t>Scope, Time &amp; Cost Impact</t>
+  </si>
+  <si>
+    <t>Verify whether each change records its effect on scope, schedule, effort and budget in actual numbers</t>
+  </si>
+  <si>
+    <t>Downstream Impact Analysis</t>
+  </si>
+  <si>
+    <t>Verify whether the assessment covers what else the change touches, including data model, interfaces, reports and tests</t>
+  </si>
+  <si>
+    <t>Approval Decision Record</t>
+  </si>
+  <si>
+    <t>Verify whether the approver, the decision, the date and any conditions attached are all recorded</t>
+  </si>
+  <si>
+    <t>Implementation Ownership</t>
+  </si>
+  <si>
+    <t>Verify whether every approved change has an implementation owner, a priority, a target date and a status</t>
+  </si>
+  <si>
+    <t>Baseline Updated</t>
+  </si>
+  <si>
+    <t>Verify whether approved changes have flowed back into the scope, plan, requirement and design baselines</t>
+  </si>
+  <si>
+    <t>Rejected CRs Retained</t>
+  </si>
+  <si>
+    <t>Verify whether rejected and deferred requests are retained along with the reason for the decision</t>
+  </si>
+  <si>
+    <t>Stakeholder Register</t>
+  </si>
+  <si>
+    <t>Stakeholder Coverage</t>
+  </si>
+  <si>
+    <t>Verify whether internal, client and third-party stakeholders are all listed with name, role and organisation</t>
+  </si>
+  <si>
+    <t>Influence &amp; Interest Rating</t>
+  </si>
+  <si>
+    <t>Verify whether each stakeholder has an assessed level of influence and interest</t>
+  </si>
+  <si>
+    <t>Engagement Approach</t>
+  </si>
+  <si>
+    <t>Verify whether each stakeholder is mapped to an engagement approach such as manage closely, keep satisfied or monitor</t>
+  </si>
+  <si>
+    <t>Channel &amp; Frequency</t>
+  </si>
+  <si>
+    <t>Verify whether the register records how often each stakeholder hears from the project and through which channel</t>
+  </si>
+  <si>
+    <t>Expectations &amp; Concerns</t>
+  </si>
+  <si>
+    <t>Verify whether the register captures what each stakeholder wants from the project and what worries them</t>
+  </si>
+  <si>
+    <t>Approval Authority Mapped</t>
+  </si>
+  <si>
+    <t>Verify whether approvers, sign-off authorities and escalation contacts are identified</t>
+  </si>
+  <si>
+    <t>Attitude Tracking</t>
+  </si>
+  <si>
+    <t>Check whether current and target stakeholder attitudes are recorded along with how the gap will be closed</t>
+  </si>
+  <si>
+    <t>Engagement Actions</t>
+  </si>
+  <si>
+    <t>Check whether specific engagement actions are documented with owners and review dates</t>
+  </si>
+  <si>
+    <t>Register Kept Current</t>
+  </si>
+  <si>
+    <t>Check whether the register is refreshed when stakeholders change roles or leave</t>
+  </si>
+  <si>
+    <t>Action Log</t>
+  </si>
+  <si>
+    <t>Action Description</t>
+  </si>
+  <si>
+    <t>Verify whether each action has an ID and a description that states the outcome expected</t>
+  </si>
+  <si>
+    <t>One Named Owner per Action</t>
+  </si>
+  <si>
+    <t>Verify whether every action names one owner</t>
+  </si>
+  <si>
+    <t>Dates &amp; Overdue Visibility</t>
+  </si>
+  <si>
+    <t>Verify whether raised and due dates are recorded and overdue items are visible</t>
+  </si>
+  <si>
+    <t>Status Kept Current</t>
+  </si>
+  <si>
+    <t>Verify whether the status column reflects where each action actually stands</t>
+  </si>
+  <si>
+    <t>Priority Classification</t>
+  </si>
+  <si>
+    <t>Verify whether actions carry a priority so critical items stand apart from routine follow-ups</t>
+  </si>
+  <si>
+    <t>Source Traceability</t>
+  </si>
+  <si>
+    <t>Verify whether each action can be traced to the meeting, decision or escalation it came from</t>
+  </si>
+  <si>
+    <t>Closure Comments</t>
+  </si>
+  <si>
+    <t>Verify whether closed actions record the closure date and what was actually done</t>
+  </si>
+  <si>
+    <t>Category Tagging</t>
+  </si>
+  <si>
+    <t>Check whether actions are tagged by type or workstream so they can be grouped</t>
+  </si>
+  <si>
+    <t>Carry-forward Escalation</t>
+  </si>
+  <si>
+    <t>Check whether actions that keep slipping are escalated rather than quietly re-dated</t>
+  </si>
+  <si>
+    <t>Open vs Closed Summary</t>
+  </si>
+  <si>
+    <t>Check whether a summary of open, in-progress and closed actions is available</t>
+  </si>
+  <si>
+    <t>Data Dictionary / KPI Glossary</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>Full Object Coverage</t>
+  </si>
+  <si>
+    <t>Verify whether every reporting table, view and column is documented</t>
+  </si>
+  <si>
+    <t>Technical Attributes</t>
+  </si>
+  <si>
+    <t>Verify whether data type, length, nullability and key designation are recorded per field</t>
+  </si>
+  <si>
+    <t>Field Business Definition</t>
+  </si>
+  <si>
+    <t>Verify whether each field has a plain-language business definition rather than a restatement of its name</t>
+  </si>
+  <si>
+    <t>Source &amp; Lineage</t>
+  </si>
+  <si>
+    <t>Verify whether the originating source and derivation lineage are identified per field</t>
+  </si>
+  <si>
+    <t>Allowed Values</t>
+  </si>
+  <si>
+    <t>Verify whether valid value sets and code lists are documented</t>
+  </si>
+  <si>
+    <t>Grain &amp; Relationships</t>
+  </si>
+  <si>
+    <t>Verify whether table grain, keys and relationships are described</t>
+  </si>
+  <si>
+    <t>Refresh Frequency</t>
+  </si>
+  <si>
+    <t>Verify whether refresh frequency and data currency are stated per object</t>
+  </si>
+  <si>
+    <t>Owners &amp; Stewards</t>
+  </si>
+  <si>
+    <t>Verify whether business owner, data steward and technical owner are named</t>
+  </si>
+  <si>
+    <t>Full KPI Inventory</t>
+  </si>
+  <si>
+    <t>Verify whether every metric exposed in reporting appears in the glossary</t>
+  </si>
+  <si>
+    <t>KPI Business Definition</t>
+  </si>
+  <si>
+    <t>Verify whether each KPI has a definition a business user could understand unaided</t>
+  </si>
+  <si>
+    <t>Calculation Formula</t>
+  </si>
+  <si>
+    <t>Verify whether the exact formula is stated, including numerator, denominator and filters</t>
+  </si>
+  <si>
+    <t>Source Tables</t>
+  </si>
+  <si>
+    <t>Verify whether the source table and attributes behind each KPI are identified</t>
+  </si>
+  <si>
+    <t>Granularity &amp; Slicing</t>
+  </si>
+  <si>
+    <t>Verify whether the granularity and the dimensions each KPI can be sliced by are documented</t>
+  </si>
+  <si>
+    <t>Time Period Definitions</t>
+  </si>
+  <si>
+    <t>Verify whether time definitions such as MTD, QTD, YTD and rolling periods are defined precisely</t>
+  </si>
+  <si>
+    <t>Inclusions &amp; Exclusions</t>
+  </si>
+  <si>
+    <t>Verify whether the records counted and the records excluded from each KPI are stated</t>
+  </si>
+  <si>
+    <t>Matches the Built Measure</t>
+  </si>
+  <si>
+    <t>Verify whether the glossary definitions match the measure logic actually running in the reporting layer</t>
+  </si>
+  <si>
+    <t>Sensitive Field Flagging</t>
+  </si>
+  <si>
+    <t>Check whether sensitive and personally identifiable fields are flagged with handling rules</t>
+  </si>
+  <si>
+    <t>Definition Change Control</t>
+  </si>
+  <si>
+    <t>Check whether definition changes go through governance and are versioned</t>
+  </si>
+  <si>
+    <t>Visual Guidance</t>
+  </si>
+  <si>
+    <t>Check whether the recommended visual type for each KPI is indicated</t>
+  </si>
+  <si>
+    <t>KPI Owner</t>
+  </si>
+  <si>
+    <t>Check whether each KPI has a business owner and approver</t>
+  </si>
+  <si>
+    <t>Implementation Plan / Rollback Plan</t>
+  </si>
+  <si>
+    <t>Release Contents</t>
+  </si>
+  <si>
+    <t>Verify whether the components, versions and changes being deployed are itemised</t>
+  </si>
+  <si>
+    <t>Team &amp; Availability</t>
+  </si>
+  <si>
+    <t>Verify whether the deployment team, contacts and their availability during the window are documented</t>
+  </si>
+  <si>
+    <t>Prerequisites &amp; Approvals</t>
+  </si>
+  <si>
+    <t>Verify whether prerequisites, approvals and code freeze confirmation are captured</t>
+  </si>
+  <si>
+    <t>Execution Runbook</t>
+  </si>
+  <si>
+    <t>Verify whether steps are sequenced with owners, durations and verification points</t>
+  </si>
+  <si>
+    <t>Backup Taken &amp; Verified</t>
+  </si>
+  <si>
+    <t>Verify whether backups were taken and verified before production was touched</t>
+  </si>
+  <si>
+    <t>Post-deployment Verification</t>
+  </si>
+  <si>
+    <t>Verify whether post-deployment checks and the criteria for restoring user access are defined</t>
+  </si>
+  <si>
+    <t>Go / No-Go Criteria</t>
+  </si>
+  <si>
+    <t>Verify whether go and no-go criteria, checkpoint timing and the decision authority are defined</t>
+  </si>
+  <si>
+    <t>Rollback Triggers</t>
+  </si>
+  <si>
+    <t>Verify whether the plan states precisely what conditions trigger a rollback</t>
+  </si>
+  <si>
+    <t>Rollback Steps</t>
+  </si>
+  <si>
+    <t>Verify whether rollback steps, sequence, owners and expected duration are documented</t>
+  </si>
+  <si>
+    <t>Post-rollback Verification</t>
+  </si>
+  <si>
+    <t>Verify whether post-rollback checks and data integrity confirmation are defined</t>
+  </si>
+  <si>
+    <t>Deployment Communications</t>
+  </si>
+  <si>
+    <t>Verify whether user notifications and status updates are planned with owners and timing</t>
+  </si>
+  <si>
+    <t>Deployment Risks</t>
+  </si>
+  <si>
+    <t>Check whether risks specific to this release and their mitigations are documented</t>
+  </si>
+  <si>
+    <t>Rollback Rehearsed</t>
+  </si>
+  <si>
+    <t>Check whether the rollback procedure was tested in a lower environment</t>
+  </si>
+  <si>
+    <t>Post-implementation Review</t>
+  </si>
+  <si>
+    <t>Check whether a post-implementation review is planned to capture lessons</t>
+  </si>
+  <si>
+    <t>Support Runbook / SOP</t>
+  </si>
+  <si>
+    <t>Hypercare</t>
+  </si>
+  <si>
+    <t>System &amp; Support Scope</t>
+  </si>
+  <si>
+    <t>Verify whether the runbook describes the system, its components and what support does and does not cover</t>
+  </si>
+  <si>
+    <t>Job Inventory &amp; Schedule</t>
+  </si>
+  <si>
+    <t>Verify whether every scheduled job is listed with its schedule, dependencies and expected duration</t>
+  </si>
+  <si>
+    <t>Operational Procedures</t>
+  </si>
+  <si>
+    <t>Verify whether routine procedures are written as steps someone could follow without prior knowledge</t>
+  </si>
+  <si>
+    <t>Failure Runbooks</t>
+  </si>
+  <si>
+    <t>Verify whether common failures carry diagnosis steps, resolution actions and post-fix validation</t>
+  </si>
+  <si>
+    <t>Restart &amp; Reprocessing</t>
+  </si>
+  <si>
+    <t>Verify whether job restart, backfill and reprocessing procedures are documented with their safeguards</t>
+  </si>
+  <si>
+    <t>Health Checks &amp; Thresholds</t>
+  </si>
+  <si>
+    <t>Verify whether monitoring points, thresholds and daily health checks are documented</t>
+  </si>
+  <si>
+    <t>Escalation Contacts</t>
+  </si>
+  <si>
+    <t>Verify whether escalation levels, named contacts and response expectations are documented</t>
+  </si>
+  <si>
+    <t>Access &amp; Credentials</t>
+  </si>
+  <si>
+    <t>Verify whether required access and credential retrieval are documented without exposing the secrets themselves</t>
+  </si>
+  <si>
+    <t>Severity &amp; Response Times</t>
+  </si>
+  <si>
+    <t>Verify whether incident severity definitions and their response and resolution times are defined</t>
+  </si>
+  <si>
+    <t>Known Issues</t>
+  </si>
+  <si>
+    <t>Check whether recurring issues and their workarounds are catalogued</t>
+  </si>
+  <si>
+    <t>Manual Intervention Control</t>
+  </si>
+  <si>
+    <t>Check whether manual interventions in production require documented approval and logging</t>
+  </si>
+  <si>
+    <t>BCP &amp; DR Procedure</t>
+  </si>
+  <si>
+    <t>Check whether failover, disaster recovery and business continuity procedures are documented or referenced</t>
+  </si>
+  <si>
+    <t>Runbook Kept Current</t>
+  </si>
+  <si>
+    <t>Check whether the runbook is version-controlled and reviewed at a set cadence</t>
+  </si>
+  <si>
+    <t>Security &amp; Compliance Assessment</t>
+  </si>
+  <si>
+    <t>Access Control Review</t>
+  </si>
+  <si>
+    <t>Verify whether authentication, role-based access, least privilege and periodic access review were assessed</t>
+  </si>
+  <si>
+    <t>Row-Level Security Tested</t>
+  </si>
+  <si>
+    <t>Verify whether row-level and object-level security were tested for isolation and cannot be bypassed</t>
+  </si>
+  <si>
+    <t>Sensitive Data Handling</t>
+  </si>
+  <si>
+    <t>Verify whether PII and sensitive fields are identified with masking or restriction controls</t>
+  </si>
+  <si>
+    <t>Encryption in Transit &amp; at Rest</t>
+  </si>
+  <si>
+    <t>Verify whether encryption standards for data in transit and at rest are documented and confirmed in place</t>
+  </si>
+  <si>
+    <t>Secret &amp; Credential Management</t>
+  </si>
+  <si>
+    <t>Verify whether credentials sit in an approved secret store with rotation, and nothing is hardcoded in code</t>
+  </si>
+  <si>
+    <t>Audit Logging &amp; Traceability</t>
+  </si>
+  <si>
+    <t>Verify whether access logs, change logs and audit trails are enabled and retained per policy</t>
+  </si>
+  <si>
+    <t>Environment Segregation</t>
+  </si>
+  <si>
+    <t>Verify whether production and non-production are segregated and production data is restricted in lower environments</t>
+  </si>
+  <si>
+    <t>Policy Mapped to Controls</t>
+  </si>
+  <si>
+    <t>Verify whether applicable regulations and client policies are mapped to the controls actually implemented</t>
+  </si>
+  <si>
+    <t>Findings Risk-Rated</t>
+  </si>
+  <si>
+    <t>Verify whether each finding carries a risk rating and its business impact</t>
+  </si>
+  <si>
+    <t>Remediation Plan</t>
+  </si>
+  <si>
+    <t>Verify whether every finding has a remediation action, owner, target date and status</t>
+  </si>
+  <si>
+    <t>Security Signed Off</t>
+  </si>
+  <si>
+    <t>Verify whether security approval was obtained before production release</t>
+  </si>
+  <si>
+    <t>Retention &amp; Disposal</t>
+  </si>
+  <si>
+    <t>Check whether retention periods and secure disposal requirements are covered</t>
+  </si>
+  <si>
+    <t>Vendor Access Risk</t>
+  </si>
+  <si>
+    <t>Check whether third-party components and vendor access risks were assessed</t>
+  </si>
+  <si>
+    <t>Reassessment Schedule</t>
+  </si>
+  <si>
+    <t>Check whether a schedule for reassessing security is defined</t>
+  </si>
+  <si>
+    <t>Learning Log</t>
+  </si>
+  <si>
+    <t>Entry Detail &amp; Clarity</t>
+  </si>
+  <si>
+    <t>Verify whether each entry says what happened, when, and who it affected in enough detail to be useful</t>
+  </si>
+  <si>
+    <t>Root Cause Analysis</t>
+  </si>
+  <si>
+    <t>Verify whether entries analyse why it happened rather than only what happened</t>
+  </si>
+  <si>
+    <t>Action Taken &amp; Outcome</t>
+  </si>
+  <si>
+    <t>Verify whether the corrective action taken and its outcome are documented</t>
+  </si>
+  <si>
+    <t>Preventive Control Added</t>
+  </si>
+  <si>
+    <t>Verify whether each learning results in a preventive control added to a checklist, standard or runbook</t>
+  </si>
+  <si>
+    <t>Category &amp; Phase</t>
+  </si>
+  <si>
+    <t>Verify whether entries are categorised by type and tagged to the phase they arose in</t>
+  </si>
+  <si>
+    <t>Owner &amp; Follow-up</t>
+  </si>
+  <si>
+    <t>Verify whether an owner and the status of the follow-up action are recorded</t>
+  </si>
+  <si>
+    <t>Logged as It Happens</t>
+  </si>
+  <si>
+    <t>Verify whether learnings were logged close to the event rather than reconstructed at project close</t>
+  </si>
+  <si>
+    <t>Impact Rating</t>
+  </si>
+  <si>
+    <t>Check whether the impact of each learning is rated</t>
+  </si>
+  <si>
+    <t>Linked to Documents</t>
+  </si>
+  <si>
+    <t>Check whether entries reference the standard or checklist that was updated as a result</t>
+  </si>
+  <si>
+    <t>Reviewed at Retros</t>
+  </si>
+  <si>
+    <t>Check whether the log is reviewed at retrospectives and reusable learnings shared more widely</t>
+  </si>
+  <si>
+    <t>Non-Functional Requirements (NFR) Document</t>
+  </si>
+  <si>
+    <t>NFR Category Coverage</t>
+  </si>
+  <si>
+    <t>Verify whether the document covers performance, availability, scalability, security, data quality, maintainability and compliance</t>
+  </si>
+  <si>
+    <t>Quantified Targets</t>
+  </si>
+  <si>
+    <t>Verify whether every NFR carries a number rather than a subjective description</t>
+  </si>
+  <si>
+    <t>Performance Targets</t>
+  </si>
+  <si>
+    <t>Verify whether batch windows, query response times, dashboard load times and refresh SLAs are quantified</t>
+  </si>
+  <si>
+    <t>Uptime &amp; Recovery Objectives</t>
+  </si>
+  <si>
+    <t>Verify whether uptime targets, maintenance windows, RTO and RPO are defined</t>
+  </si>
+  <si>
+    <t>Volume &amp; Growth Assumptions</t>
+  </si>
+  <si>
+    <t>Verify whether current volumes, projected growth and concurrent user load are stated</t>
+  </si>
+  <si>
+    <t>Security Requirements</t>
+  </si>
+  <si>
+    <t>Verify whether authentication, authorisation, row-level security, encryption and PII handling requirements are specified</t>
+  </si>
+  <si>
+    <t>Data Quality Thresholds</t>
+  </si>
+  <si>
+    <t>Verify whether accuracy, completeness, timeliness and reconciliation tolerances are quantified</t>
+  </si>
+  <si>
+    <t>Monitoring &amp; Alerting</t>
+  </si>
+  <si>
+    <t>Verify whether logging, monitoring, alert thresholds and supportability requirements are specified</t>
+  </si>
+  <si>
+    <t>Backup &amp; Restore</t>
+  </si>
+  <si>
+    <t>Verify whether backup frequency, restore procedure and archival requirements carry measurable targets</t>
+  </si>
+  <si>
+    <t>NFR Testability</t>
+  </si>
+  <si>
+    <t>Verify whether each NFR says how it will be tested, in which environment, and what counts as a pass</t>
+  </si>
+  <si>
+    <t>Priority &amp; Trade-offs</t>
+  </si>
+  <si>
+    <t>Check whether NFRs are prioritised and any trade-off between competing ones is explained</t>
+  </si>
+  <si>
+    <t>NFR Ownership</t>
+  </si>
+  <si>
+    <t>Check whether each NFR area has a named owner and approver</t>
+  </si>
+  <si>
+    <t>Technical Design Document</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Architecture &amp; Rationale</t>
+  </si>
+  <si>
+    <t>Verify whether the document explains not only the architecture but why that approach was chosen</t>
+  </si>
+  <si>
+    <t>Source Extract Design</t>
+  </si>
+  <si>
+    <t>Verify whether each source names its connection method, extraction strategy and how incremental data is identified</t>
+  </si>
+  <si>
+    <t>Schema &amp; Grain Design</t>
+  </si>
+  <si>
+    <t>Verify whether the target schema, keys, grain, relationships and slowly changing dimension handling are documented</t>
+  </si>
+  <si>
+    <t>Transformation Design</t>
+  </si>
+  <si>
+    <t>Verify whether the transformation layers and the way business rules are implemented are specified</t>
+  </si>
+  <si>
+    <t>Orchestration &amp; Dependencies</t>
+  </si>
+  <si>
+    <t>Verify whether job orchestration, schedules, dependencies and failure behaviour are defined</t>
+  </si>
+  <si>
+    <t>Reporting Layer Design</t>
+  </si>
+  <si>
+    <t>Verify whether dataset design, connection mode, measure standards and report performance approach are documented</t>
+  </si>
+  <si>
+    <t>Error Handling &amp; Reconciliation</t>
+  </si>
+  <si>
+    <t>Verify whether error handling, retry logic, audit tables and source-to-target reconciliation are designed</t>
+  </si>
+  <si>
+    <t>Performance Design</t>
+  </si>
+  <si>
+    <t>Verify whether partitioning, indexing, incremental processing and growth headroom are addressed</t>
+  </si>
+  <si>
+    <t>Naming Standards</t>
+  </si>
+  <si>
+    <t>Verify whether naming conventions for objects, jobs, models and code artefacts are defined</t>
+  </si>
+  <si>
+    <t>Environment &amp; CI/CD Design</t>
+  </si>
+  <si>
+    <t>Verify whether environment topology, branching, code promotion and deployment automation are documented</t>
+  </si>
+  <si>
+    <t>Design Approved Before Build</t>
+  </si>
+  <si>
+    <t>Verify whether architecture and client approval were obtained before development started</t>
+  </si>
+  <si>
+    <t>End-to-End Components</t>
+  </si>
+  <si>
+    <t>Verify whether the diagram shows everything from source systems through to consumption</t>
+  </si>
+  <si>
+    <t>Layer Separation</t>
+  </si>
+  <si>
+    <t>Verify whether the raw, cleansed and curated layers are drawn as distinct zones</t>
+  </si>
+  <si>
+    <t>Environment Boundaries</t>
+  </si>
+  <si>
+    <t>Verify whether development, test and production environments and their boundaries are visible</t>
+  </si>
+  <si>
+    <t>Flow Direction &amp; Protocol</t>
+  </si>
+  <si>
+    <t>Verify whether connections show the direction of flow and how the interaction happens</t>
+  </si>
+  <si>
+    <t>Security Components</t>
+  </si>
+  <si>
+    <t>Verify whether the identity provider, secret store, network boundaries and access control points are drawn</t>
+  </si>
+  <si>
+    <t>Platform Labelling</t>
+  </si>
+  <si>
+    <t>Verify whether each component is labelled with the actual platform or service in use</t>
+  </si>
+  <si>
+    <t>Consumers &amp; Outbound Feeds</t>
+  </si>
+  <si>
+    <t>Verify whether reporting layers, downstream consumers and outbound feeds are represented</t>
+  </si>
+  <si>
+    <t>Legend &amp; Readability</t>
+  </si>
+  <si>
+    <t>Verify whether a legend explains the notation and the labelling is legible</t>
+  </si>
+  <si>
+    <t>Entities &amp; Relationships</t>
+  </si>
+  <si>
+    <t>Verify whether entities, attributes and relationships are defined with cardinality marked</t>
+  </si>
+  <si>
+    <t>Logical &amp; Physical Models</t>
+  </si>
+  <si>
+    <t>Verify whether both a logical and a physical model exist and agree with each other</t>
+  </si>
+  <si>
+    <t>Keys &amp; Constraints</t>
+  </si>
+  <si>
+    <t>Verify whether primary keys, foreign keys, unique constraints and indexes are specified</t>
+  </si>
+  <si>
+    <t>Fact Grain Defined</t>
+  </si>
+  <si>
+    <t>Verify whether the grain of each fact table is stated and shared dimensions are conformed</t>
+  </si>
+  <si>
+    <t>Types &amp; Naming Standards</t>
+  </si>
+  <si>
+    <t>Verify whether data types, lengths and object naming follow the agreed standard</t>
+  </si>
+  <si>
+    <t>Historisation Approach</t>
+  </si>
+  <si>
+    <t>Verify whether the historisation approach is specified for each entity that changes over time</t>
+  </si>
+  <si>
+    <t>Alternatives Considered</t>
+  </si>
+  <si>
+    <t>Check whether alternatives were considered and the reason for the chosen option is recorded</t>
+  </si>
+  <si>
+    <t>Infrastructure Sizing</t>
+  </si>
+  <si>
+    <t>Check whether environment configuration, compute sizing and running cost are documented</t>
+  </si>
+  <si>
+    <t>Orchestration &amp; CI/CD</t>
+  </si>
+  <si>
+    <t>Check whether orchestration, scheduling and deployment pipelines are depicted</t>
+  </si>
+  <si>
+    <t>Monitoring Components</t>
+  </si>
+  <si>
+    <t>Check whether monitoring, logging and alerting components appear on the diagram</t>
+  </si>
+  <si>
+    <t>HA &amp; DR Representation</t>
+  </si>
+  <si>
+    <t>Check whether redundancy, failover or disaster recovery components are shown</t>
+  </si>
+  <si>
+    <t>Matches Deployed Schema</t>
+  </si>
+  <si>
+    <t>Check whether the model matches the schema actually deployed, including post-approval changes</t>
+  </si>
+  <si>
+    <t>Volumetrics per Entity</t>
+  </si>
+  <si>
+    <t>Check whether expected row counts and growth are documented per entity</t>
+  </si>
+  <si>
+    <t>Integration Design</t>
+  </si>
+  <si>
+    <t>Interface Inventory</t>
+  </si>
+  <si>
+    <t>Verify whether every inbound and outbound interface is inventoried with an ID and description</t>
+  </si>
+  <si>
+    <t>Source &amp; Target Objects</t>
+  </si>
+  <si>
+    <t>Verify whether each interface names its source system, source object, target system and target object</t>
+  </si>
+  <si>
+    <t>Pattern &amp; Load Type</t>
+  </si>
+  <si>
+    <t>Verify whether each interface states its pattern, such as batch, incremental, full load or API</t>
+  </si>
+  <si>
+    <t>Trigger &amp; Schedule</t>
+  </si>
+  <si>
+    <t>Verify whether triggers, schedules, refresh frequency and expected volumes are documented</t>
+  </si>
+  <si>
+    <t>Field-level Mapping</t>
+  </si>
+  <si>
+    <t>Verify whether mapping is specified at field level with data types, nullability and transformation rules</t>
+  </si>
+  <si>
+    <t>File &amp; API Contract</t>
+  </si>
+  <si>
+    <t>Verify whether file formats, delimiters, naming patterns and API contracts are specified</t>
+  </si>
+  <si>
+    <t>Error Handling &amp; Retry</t>
+  </si>
+  <si>
+    <t>Verify whether each interface defines its error scenarios, retry logic and alert routing</t>
+  </si>
+  <si>
+    <t>Reconciliation Controls</t>
+  </si>
+  <si>
+    <t>Verify whether row counts and reconciliation checkpoints between source and target are defined</t>
+  </si>
+  <si>
+    <t>Interface Ownership</t>
+  </si>
+  <si>
+    <t>Verify whether interface owners, upstream dependencies and third-party responsibilities are identified</t>
+  </si>
+  <si>
+    <t>Latency &amp; Processing Window</t>
+  </si>
+  <si>
+    <t>Check whether expected latency and processing windows are quantified</t>
+  </si>
+  <si>
+    <t>Interface Build Status</t>
+  </si>
+  <si>
+    <t>Check whether build and test status is tracked per interface</t>
+  </si>
+  <si>
+    <t>Data Flow Diagram</t>
+  </si>
+  <si>
+    <t>Source to Consumption</t>
+  </si>
+  <si>
+    <t>Verify whether the diagram traces data from every source through to final consumption</t>
+  </si>
+  <si>
+    <t>Processing Stages</t>
+  </si>
+  <si>
+    <t>Verify whether each processing stage and the transitions between layers are represented</t>
+  </si>
+  <si>
+    <t>Dataset Labelling</t>
+  </si>
+  <si>
+    <t>Verify whether objects at each stage are named rather than shown as generic boxes</t>
+  </si>
+  <si>
+    <t>Direction &amp; Frequency</t>
+  </si>
+  <si>
+    <t>Verify whether each flow shows its direction and how often it runs</t>
+  </si>
+  <si>
+    <t>Rule Application Points</t>
+  </si>
+  <si>
+    <t>Verify whether the points where transformations or business rules apply are identified</t>
+  </si>
+  <si>
+    <t>Downstream Consumers</t>
+  </si>
+  <si>
+    <t>Verify whether outbound extracts, downstream systems and report consumers appear on the diagram</t>
+  </si>
+  <si>
+    <t>DQ Checkpoints Shown</t>
+  </si>
+  <si>
+    <t>Check whether data quality and validation checkpoints are marked within the flow</t>
+  </si>
+  <si>
+    <t>Overview &amp; Detail Views</t>
+  </si>
+  <si>
+    <t>Check whether both an overview and a detailed view are provided</t>
+  </si>
+  <si>
+    <t>Wireframes / Figma for Dashboard</t>
+  </si>
+  <si>
+    <t>All Screens Covered</t>
+  </si>
+  <si>
+    <t>Verify whether a wireframe exists for every dashboard, screen and navigation page in scope</t>
+  </si>
+  <si>
+    <t>KPI &amp; Visual Placement</t>
+  </si>
+  <si>
+    <t>Verify whether each KPI and chart is placed on the layout with its intended visual type</t>
+  </si>
+  <si>
+    <t>Filters &amp; Navigation</t>
+  </si>
+  <si>
+    <t>Verify whether filters, default selections, drill paths and navigation controls are shown</t>
+  </si>
+  <si>
+    <t>Layout &amp; Canvas Spec</t>
+  </si>
+  <si>
+    <t>Verify whether canvas size, grid alignment and spacing are specified</t>
+  </si>
+  <si>
+    <t>Interaction Behaviour</t>
+  </si>
+  <si>
+    <t>Verify whether cross-filtering, drill-through, tooltip and bookmark behaviour is described</t>
+  </si>
+  <si>
+    <t>Traceable to KPIs</t>
+  </si>
+  <si>
+    <t>Verify whether each visual maps to an approved requirement or KPI definition</t>
+  </si>
+  <si>
+    <t>Client Sign-off Before Build</t>
+  </si>
+  <si>
+    <t>Verify whether business stakeholders approved the wireframes before development began</t>
+  </si>
+  <si>
+    <t>Style Guide Adherence</t>
+  </si>
+  <si>
+    <t>Check whether fonts, colour palette and component styling follow the agreed style guide</t>
+  </si>
+  <si>
+    <t>Readability &amp; Accessibility</t>
+  </si>
+  <si>
+    <t>Check whether readability, colour contrast and usability have been considered</t>
+  </si>
+  <si>
+    <t>Empty &amp; Error States</t>
+  </si>
+  <si>
+    <t>Check whether no-data, loading and error states are depicted</t>
+  </si>
+  <si>
+    <t>Wireframe Versions</t>
+  </si>
+  <si>
+    <t>Check whether wireframe versions and feedback rounds are tracked</t>
+  </si>
+  <si>
+    <t>Source to Target Mapping (STTM)</t>
+  </si>
+  <si>
+    <t>Every Target Field Mapped</t>
+  </si>
+  <si>
+    <t>Verify whether every target field has a source field or an explicitly stated derivation</t>
+  </si>
+  <si>
+    <t>Source &amp; Target Named</t>
+  </si>
+  <si>
+    <t>Verify whether each mapping names its source system, source object, target schema and target table</t>
+  </si>
+  <si>
+    <t>Types &amp; Conversion Rules</t>
+  </si>
+  <si>
+    <t>Verify whether data types and lengths on both sides are stated along with any conversion rule</t>
+  </si>
+  <si>
+    <t>Derivation Logic</t>
+  </si>
+  <si>
+    <t>Verify whether derived fields carry the actual rule rather than a description of it</t>
+  </si>
+  <si>
+    <t>Keys, Grain &amp; Joins</t>
+  </si>
+  <si>
+    <t>Verify whether business keys, join conditions and record grain are defined</t>
+  </si>
+  <si>
+    <t>Null &amp; Default Handling</t>
+  </si>
+  <si>
+    <t>Verify whether nullability, default values and handling of invalid data are specified</t>
+  </si>
+  <si>
+    <t>Load Type &amp; History</t>
+  </si>
+  <si>
+    <t>Verify whether load type, incremental keys, deduplication and historisation treatment are specified</t>
+  </si>
+  <si>
+    <t>Filters &amp; Delete Handling</t>
+  </si>
+  <si>
+    <t>Verify whether record filters, exclusions and delete handling are documented</t>
+  </si>
+  <si>
+    <t>Traceable to Requirements</t>
+  </si>
+  <si>
+    <t>Check whether mappings tie back to requirement or business rule identifiers</t>
+  </si>
+  <si>
+    <t>Points to a Data Model</t>
+  </si>
+  <si>
+    <t>Check whether the mapping references an approved physical data model rather than standing in for one</t>
+  </si>
+  <si>
+    <t>Unit Testing Document</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>Component Coverage</t>
+  </si>
+  <si>
+    <t>Verify whether every built component has at least one test, including extracts, transformations, measures and security roles</t>
+  </si>
+  <si>
+    <t>Test ID &amp; Description</t>
+  </si>
+  <si>
+    <t>Verify whether each test carries an ID, the module under test and what it validates</t>
+  </si>
+  <si>
+    <t>Expected Result Stated</t>
+  </si>
+  <si>
+    <t>Verify whether a precise expected result was stated for each test</t>
+  </si>
+  <si>
+    <t>Inputs &amp; Pre-conditions</t>
+  </si>
+  <si>
+    <t>Verify whether inputs, pre-conditions and test data are documented well enough to re-run the test</t>
+  </si>
+  <si>
+    <t>Actual Result &amp; Status</t>
+  </si>
+  <si>
+    <t>Verify whether actual results and pass or fail status are recorded for every test</t>
+  </si>
+  <si>
+    <t>Negative &amp; Boundary Cases</t>
+  </si>
+  <si>
+    <t>Verify whether nulls, duplicates, invalid inputs and boundary values were tested alongside the clean cases</t>
+  </si>
+  <si>
+    <t>Execution Evidence</t>
+  </si>
+  <si>
+    <t>Verify whether tester name, execution date and supporting evidence such as query output are captured</t>
+  </si>
+  <si>
+    <t>Defect Link &amp; Retest</t>
+  </si>
+  <si>
+    <t>Verify whether failed tests link to a defect and show a retest result after the fix</t>
+  </si>
+  <si>
+    <t>Signed Off Before SIT</t>
+  </si>
+  <si>
+    <t>Verify whether unit testing was signed off before the build was handed to system testing</t>
+  </si>
+  <si>
+    <t>Repeatable Tests</t>
+  </si>
+  <si>
+    <t>Check whether tests are automated or scripted so they can be re-run on demand</t>
+  </si>
+  <si>
+    <t>Coverage by Module</t>
+  </si>
+  <si>
+    <t>Check whether coverage or completeness is reported by module or layer</t>
+  </si>
+  <si>
+    <t>Pass Rate Summary</t>
+  </si>
+  <si>
+    <t>Check whether an aggregated pass rate is available</t>
+  </si>
+  <si>
+    <t>Defect Log/Incident Tracker</t>
+  </si>
+  <si>
+    <t>Defect Description</t>
+  </si>
+  <si>
+    <t>Verify whether each defect states what was observed against what was expected</t>
+  </si>
+  <si>
+    <t>Steps to Reproduce</t>
+  </si>
+  <si>
+    <t>Verify whether steps to reproduce, environment, build version and evidence are captured</t>
+  </si>
+  <si>
+    <t>Severity &amp; Priority</t>
+  </si>
+  <si>
+    <t>Verify whether severity and priority are assigned using defined criteria rather than judgement in the moment</t>
+  </si>
+  <si>
+    <t>Module &amp; Test Case Link</t>
+  </si>
+  <si>
+    <t>Verify whether each defect links to the affected module, the test case that found it and the testing phase</t>
+  </si>
+  <si>
+    <t>Raised By &amp; Assigned To</t>
+  </si>
+  <si>
+    <t>Verify whether raised-by and assigned-to are recorded</t>
+  </si>
+  <si>
+    <t>Root Cause Recorded</t>
+  </si>
+  <si>
+    <t>Verify whether resolved defects record the root cause and not only the fix applied</t>
+  </si>
+  <si>
+    <t>Fix Build &amp; Retest</t>
+  </si>
+  <si>
+    <t>Verify whether resolution details, fix build, retest outcome and closure date are recorded</t>
+  </si>
+  <si>
+    <t>Status Discipline</t>
+  </si>
+  <si>
+    <t>Verify whether statuses follow a defined lifecycle with nothing left stale or ambiguous</t>
+  </si>
+  <si>
+    <t>Defect Ageing</t>
+  </si>
+  <si>
+    <t>Check whether defect ageing is tracked against the agreed resolution times</t>
+  </si>
+  <si>
+    <t>Defect Trend Analysis</t>
+  </si>
+  <si>
+    <t>Check whether defects are grouped by type and analysed for recurring patterns</t>
+  </si>
+  <si>
+    <t>Defect Leakage</t>
+  </si>
+  <si>
+    <t>Check whether defects found late or after go-live are traced back to the phase that should have caught them</t>
+  </si>
+  <si>
+    <t>Defect Summary View</t>
+  </si>
+  <si>
+    <t>Check whether a summary by severity, status and module is available</t>
+  </si>
+  <si>
+    <t>UAT Test Case Document / Expected Results</t>
+  </si>
+  <si>
+    <t>UAT</t>
+  </si>
+  <si>
+    <t>Business Scenario Coverage</t>
+  </si>
+  <si>
+    <t>Verify whether scenarios cover every critical business process, KPI, report and user journey in scope</t>
+  </si>
+  <si>
+    <t>Written in Business Language</t>
+  </si>
+  <si>
+    <t>Verify whether scenarios are written the way a business user works rather than as technical steps</t>
+  </si>
+  <si>
+    <t>Pre-conditions &amp; Role</t>
+  </si>
+  <si>
+    <t>Verify whether pre-conditions, user role, access setup and data period are specified</t>
+  </si>
+  <si>
+    <t>Step-by-step Instructions</t>
+  </si>
+  <si>
+    <t>Verify whether the steps are numbered and clear enough for a business user to run unaided</t>
+  </si>
+  <si>
+    <t>Acceptance Criteria</t>
+  </si>
+  <si>
+    <t>Verify whether each scenario says precisely what a pass looks like</t>
+  </si>
+  <si>
+    <t>Expected vs Actual</t>
+  </si>
+  <si>
+    <t>Verify whether expected results, actual results and status are recorded per scenario</t>
+  </si>
+  <si>
+    <t>Access Scenarios Tested</t>
+  </si>
+  <si>
+    <t>Verify whether scenarios test that users see only the data their role permits</t>
+  </si>
+  <si>
+    <t>Verify whether failed scenarios link to a defect and show a retest outcome</t>
+  </si>
+  <si>
+    <t>Tester &amp; Date</t>
+  </si>
+  <si>
+    <t>Verify whether the client tester's name and the execution date are captured</t>
+  </si>
+  <si>
+    <t>Grouped by Business Area</t>
+  </si>
+  <si>
+    <t>Check whether scenarios are grouped by business area, module or user role</t>
+  </si>
+  <si>
+    <t>Edge Scenarios</t>
+  </si>
+  <si>
+    <t>Check whether unusual or exception business scenarios are included</t>
+  </si>
+  <si>
+    <t>UAT Deck</t>
+  </si>
+  <si>
+    <t>UAT Session Conducted</t>
+  </si>
+  <si>
+    <t>Verify whether the UAT walkthrough session was held, with the date and participants recorded</t>
+  </si>
+  <si>
+    <t>Entry Criteria Confirmed</t>
+  </si>
+  <si>
+    <t>Verify whether the deck confirms SIT completion, environment readiness and test data availability before UAT began</t>
+  </si>
+  <si>
+    <t>Demo &amp; Walkthrough Coverage</t>
+  </si>
+  <si>
+    <t>Verify whether the deck evidences a walkthrough of every dashboard, report or module in scope</t>
+  </si>
+  <si>
+    <t>Defect Summary Presented</t>
+  </si>
+  <si>
+    <t>Verify whether open defects with their severity and status were presented to the business</t>
+  </si>
+  <si>
+    <t>Exit Criteria Defined</t>
+  </si>
+  <si>
+    <t>Verify whether the deck states the UAT exit criteria and the route to formal sign-off</t>
+  </si>
+  <si>
+    <t>UAT Scope &amp; Period</t>
+  </si>
+  <si>
+    <t>Verify whether the register states what was tested, in which environment and over what data period</t>
+  </si>
+  <si>
+    <t>Execution Summary</t>
+  </si>
+  <si>
+    <t>Verify whether the register summarises scenarios executed, passed, failed and deferred</t>
+  </si>
+  <si>
+    <t>Open Defects at Sign-off</t>
+  </si>
+  <si>
+    <t>Verify whether every defect still open at sign-off is listed with its severity and agreed disposition</t>
+  </si>
+  <si>
+    <t>Deferred Items Agreed</t>
+  </si>
+  <si>
+    <t>Verify whether deferred items carry an owner, a target release and explicit business acceptance</t>
+  </si>
+  <si>
+    <t>Approver Authority</t>
+  </si>
+  <si>
+    <t>Verify whether the person signing holds the authority to accept on behalf of the business</t>
+  </si>
+  <si>
+    <t>Written Sign-off</t>
+  </si>
+  <si>
+    <t>Verify whether sign-off is documented with name, role and date</t>
+  </si>
+  <si>
+    <t>Conditions of Acceptance</t>
+  </si>
+  <si>
+    <t>Verify whether any conditions attached to the acceptance are stated</t>
+  </si>
+  <si>
+    <t>Go-live Readiness</t>
+  </si>
+  <si>
+    <t>Verify whether the register confirms readiness to proceed to deployment</t>
+  </si>
+  <si>
+    <t>Training &amp; Enablement Covered</t>
+  </si>
+  <si>
+    <t>Check whether user training, navigation guidance or enablement material is included</t>
+  </si>
+  <si>
+    <t>Feedback &amp; Follow-up Actions</t>
+  </si>
+  <si>
+    <t>Check whether business feedback raised during UAT is listed with owners and target dates</t>
+  </si>
+  <si>
+    <t>Sign-off by Business Area</t>
+  </si>
+  <si>
+    <t>Check whether sign-off is recorded separately for each business area or module</t>
+  </si>
+  <si>
+    <t>Residual Risk Accepted</t>
+  </si>
+  <si>
+    <t>Check whether residual risks accepted by the business are acknowledged</t>
+  </si>
+  <si>
+    <t>Project Closure Deck / RTM</t>
+  </si>
+  <si>
+    <t>Scope Delivered vs Committed</t>
+  </si>
+  <si>
+    <t>Verify whether the deck shows what was committed at the start against what was actually delivered, with any variance explained</t>
+  </si>
+  <si>
+    <t>Deliverable Handover Status</t>
+  </si>
+  <si>
+    <t>Verify whether every deliverable is listed with its final status and confirmation that it has been handed over to the client</t>
+  </si>
+  <si>
+    <t>Milestone &amp; Timeline Summary</t>
+  </si>
+  <si>
+    <t>Verify whether planned against actual dates are shown for the key milestones, with reasons for any slippage</t>
+  </si>
+  <si>
+    <t>Success Criteria Achievement</t>
+  </si>
+  <si>
+    <t>Verify whether the success criteria agreed at initiation are restated and evidenced as met, partially met or not met</t>
+  </si>
+  <si>
+    <t>Open Items &amp; Deferred Scope</t>
+  </si>
+  <si>
+    <t>Verify whether items still open or deferred at closure are listed with an owner, a target and explicit client agreement</t>
+  </si>
+  <si>
+    <t>Defect Status at Closure</t>
+  </si>
+  <si>
+    <t>Verify whether outstanding defects are shown with severity and the agreed disposition for each</t>
+  </si>
+  <si>
+    <t>Support Transition &amp; Ownership</t>
+  </si>
+  <si>
+    <t>Verify whether the deck states who supports the solution after closure, from when, and how issues should be raised</t>
+  </si>
+  <si>
+    <t>Formal Closure Sign-off</t>
+  </si>
+  <si>
+    <t>Verify whether the deck carries formal client acceptance of project closure with an approver name, role and date</t>
+  </si>
+  <si>
+    <t>End-to-End Traceability</t>
+  </si>
+  <si>
+    <t>Verify whether a single requirement can be followed through design, build, test case and UAT to closure</t>
+  </si>
+  <si>
+    <t>Requirement ID Discipline</t>
+  </si>
+  <si>
+    <t>Verify whether each requirement carries a unique ID used consistently across every downstream document</t>
+  </si>
+  <si>
+    <t>Two-way Traceability</t>
+  </si>
+  <si>
+    <t>Verify whether every requirement maps to a test case and every test case maps back to a requirement</t>
+  </si>
+  <si>
+    <t>Coverage Gaps Visible</t>
+  </si>
+  <si>
+    <t>Verify whether requirements with no design, build or test coverage stand out rather than blending in</t>
+  </si>
+  <si>
+    <t>CRs Added to Matrix</t>
+  </si>
+  <si>
+    <t>Verify whether approved change requests are added to the matrix with the same traceability as original requirements</t>
+  </si>
+  <si>
+    <t>Requirement Status Tracking</t>
+  </si>
+  <si>
+    <t>Verify whether each requirement is tracked through to accepted</t>
+  </si>
+  <si>
+    <t>Effort &amp; Budget Summary</t>
+  </si>
+  <si>
+    <t>Check whether final effort and budget against plan are summarised for the client</t>
+  </si>
+  <si>
+    <t>Lessons Learned Shared</t>
+  </si>
+  <si>
+    <t>Check whether key lessons from the engagement are shared rather than kept internal</t>
+  </si>
+  <si>
+    <t>Client Feedback Captured</t>
+  </si>
+  <si>
+    <t>Check whether client feedback or a satisfaction input was requested and recorded at closure</t>
+  </si>
+  <si>
+    <t>Next Phase &amp; Enhancement Outlook</t>
+  </si>
+  <si>
+    <t>Check whether known enhancements, Phase 2 scope or roadmap items are outlined</t>
+  </si>
+  <si>
+    <t>Priority Tagging</t>
+  </si>
+  <si>
+    <t>Check whether requirements are tagged by priority so critical coverage can be confirmed first</t>
+  </si>
+  <si>
+    <t>Descoped Items Visible</t>
+  </si>
+  <si>
+    <t>Check whether descoped or deferred requirements remain visible with the rationale and decision owner</t>
+  </si>
+  <si>
+    <t>Pricing Tool / Finance Document (Cost Estimator/WLBU)</t>
+  </si>
+  <si>
+    <t>Current Template &amp; Rate Card</t>
+  </si>
+  <si>
+    <t>Verify whether the estimate uses the current pricing template and the rate card version named on the rate card tab</t>
+  </si>
+  <si>
+    <t>Project Dates &amp; Duration</t>
+  </si>
+  <si>
+    <t>Verify whether project name, start date and end date are filled in and agree with the SOW</t>
+  </si>
+  <si>
+    <t>Resource Plan Completeness</t>
+  </si>
+  <si>
+    <t>Verify whether every resource line carries a location, position and domain, since that combination drives the rate lookup</t>
+  </si>
+  <si>
+    <t>Week-wise Effort Phasing</t>
+  </si>
+  <si>
+    <t>Verify whether hours are phased week by week, with nothing planned outside the project start and end dates</t>
+  </si>
+  <si>
+    <t>Rate Card Integrity</t>
+  </si>
+  <si>
+    <t>Verify whether billing and cost rates come from the locked rate card, with no manual overrides</t>
+  </si>
+  <si>
+    <t>Gross Margin Threshold</t>
+  </si>
+  <si>
+    <t>Verify whether the proposed gross margin clears 40 percent, and if not, whether a written commercial justification exists</t>
+  </si>
+  <si>
+    <t>Discount Threshold</t>
+  </si>
+  <si>
+    <t>Verify whether the discount stays within 10 percent, and if it does not, whether the prior Partner approval is on file</t>
+  </si>
+  <si>
+    <t>High-Value Approval Routing</t>
+  </si>
+  <si>
+    <t>Verify whether high-value deals with margin below the benchmark went for pricing review and Partner approval before the proposal left</t>
+  </si>
+  <si>
+    <t>Blended Rate Sanity Check</t>
+  </si>
+  <si>
+    <t>Verify whether the blended billing rate is calculated correctly and looks sensible against comparable engagements</t>
+  </si>
+  <si>
+    <t>Onshore-Offshore Mix</t>
+  </si>
+  <si>
+    <t>Verify whether the offshore share and the seniority pyramid are realistic for the work being priced</t>
+  </si>
+  <si>
+    <t>SOW Commercial Alignment</t>
+  </si>
+  <si>
+    <t>Verify whether duration, resourcing, discount and estimate all match the executed SOW</t>
+  </si>
+  <si>
+    <t>Functional Requirement Document (FRD/FSD/FRS)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,10 +2592,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -512,12 +2612,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -595,7 +2695,18 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -610,7 +2721,18 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -619,7 +2741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -627,16 +2749,28 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -976,388 +3110,575 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{146FE398-1690-4180-AF13-DDDB6EDC0F95}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="90.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.77734375" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="89.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="90.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>90</v>
+    </row>
+    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -1366,15 +3687,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25298CCA-7545-47FF-9B14-D6E27C46C990}">
-  <dimension ref="A1:E45"/>
-  <sheetFormatPr defaultColWidth="90.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B5FC0E-D7D1-4134-97F1-75A2EB32763F}">
+  <dimension ref="A1:E370"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" customWidth="1"/>
-    <col min="2" max="2" width="29.77734375" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="89.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="110.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1382,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -1394,576 +3715,576 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>843</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>4</v>
+        <v>843</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="4" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="4" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="B19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="4" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="4" t="s">
+    </row>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="4" t="s">
+    </row>
+    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="4" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="4" t="s">
+    </row>
+    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="4" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="4" t="s">
+    </row>
+    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="4" t="s">
+    </row>
+    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="4" t="s">
+    </row>
+    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+    </row>
+    <row r="29" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="E29" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="4" t="s">
+    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E31" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="4" t="s">
+    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="4" t="s">
+    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="4" t="s">
+    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>118</v>
@@ -1972,177 +4293,5700 @@
         <v>119</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="4" t="s">
+    <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="4" t="s">
+    <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E50" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="4" t="s">
+    <row r="51" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E51" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="4" t="s">
+    <row r="52" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E52" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E45" s="6" t="s">
+    <row r="53" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="8"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="E165" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="E166" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A173" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A175" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A191" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A193" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A194" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A195" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A196" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A198" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A199" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A200" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A201" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A202" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A203" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A204" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A205" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="E207" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="E208" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="E209" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A210" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E210" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A211" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="E211" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A212" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="E212" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A213" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E213" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A214" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="E214" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A215" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B215" s="4" t="s">
         <v>139</v>
       </c>
+      <c r="C215" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E215" s="4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A216" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="E216" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A217" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E217" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A218" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="E218" s="4" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A219" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="E219" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A220" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="E220" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A221" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E221" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A222" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="E222" s="4" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A223" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E223" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A224" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="E224" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A225" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="E225" s="4" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A226" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D227" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="E227" s="4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A228" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="E228" s="4" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A229" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="E229" s="4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A230" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="E230" s="4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A231" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E231" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A232" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="E232" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A233" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="E233" s="4" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A234" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="E234" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A235" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="E235" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A236" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E236" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A237" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E237" s="4" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A238" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="E238" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A239" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="E239" s="4" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A240" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="E240" s="4" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A241" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="E241" s="4" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A242" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="E242" s="4" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A243" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E243" s="4" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A244" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E244" s="4" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A245" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="E245" s="4" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A246" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E246" s="4" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A247" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="E247" s="4" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A248" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="E248" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A249" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D249" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E249" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A250" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="E250" s="4" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A251" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="E251" s="4" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A252" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E252" s="4" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A253" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A254" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A255" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="E255" s="4" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A256" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="E256" s="4" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A257" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="E257" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A258" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="E258" s="4" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A259" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="E259" s="4" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A260" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="E260" s="4" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A261" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="E261" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A262" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="E262" s="4" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A263" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D263" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="E263" s="4" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A264" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="E264" s="4" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A265" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="E265" s="4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A266" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="E266" s="4" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A267" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="E267" s="4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A268" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="E268" s="4" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A269" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="E269" s="4" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A270" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E270" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A271" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="E271" s="4" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A272" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="E272" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A273" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D273" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E273" s="4" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A274" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="E274" s="4" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A275" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D275" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="E275" s="4" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A276" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D276" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="E276" s="4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A277" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D277" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E277" s="4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A278" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D278" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="E278" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A279" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D279" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="E279" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A280" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D280" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="E280" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A281" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D281" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="E281" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A282" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D282" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="E282" s="4" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A283" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D283" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="E283" s="4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A284" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D284" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="E284" s="4" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A285" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D285" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="E285" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A286" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D286" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="E286" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A287" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D287" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="E287" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A288" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D288" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="E288" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A289" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="E289" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A290" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="E290" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A291" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D291" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="E291" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A292" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D292" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="E292" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A293" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D293" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="E293" s="4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A294" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="E294" s="4" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A295" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="E295" s="4" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A296" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="E296" s="4" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A297" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D297" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="E297" s="4" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A298" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="E298" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A299" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="E299" s="4" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A300" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="E300" s="4" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A301" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="E301" s="4" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A302" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="E302" s="4" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A303" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="E303" s="4" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A304" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="E304" s="4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A305" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="E305" s="4" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A306" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E306" s="4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A307" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="E307" s="4" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A308" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E308" s="4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A309" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="E309" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A310" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A311" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A312" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="E312" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A313" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="E313" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A314" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="E314" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A315" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="E315" s="4" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A316" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="E316" s="4" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A317" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="E317" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A318" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A319" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="E319" s="4" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A320" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="E320" s="4" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A321" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="E321" s="4" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A322" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="E322" s="4" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A323" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D323" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="E323" s="4" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A324" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D324" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="E324" s="4" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A325" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D325" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="E325" s="4" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A326" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D326" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="E326" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A327" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="E327" s="4" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A328" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E328" s="4" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A329" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="E329" s="4" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A330" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E330" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A331" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D331" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="E331" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A332" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D332" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="E332" s="4" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A333" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D333" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="E333" s="4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A334" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D334" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="E334" s="4" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A335" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D335" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="E335" s="4" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A336" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D336" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="E336" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A337" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D337" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="E337" s="4" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A338" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D338" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="E338" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A339" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D339" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="E339" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A340" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D340" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="E340" s="4" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A341" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D341" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="E341" s="4" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A342" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D342" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="E342" s="4" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A343" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D343" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="E343" s="4" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A344" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D344" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="E344" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A345" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D345" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="E345" s="4" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A346" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D346" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="E346" s="4" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A347" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D347" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="E347" s="4" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A348" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B348" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D348" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="E348" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A349" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D349" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="E349" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A350" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="E350" s="4" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A351" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D351" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="E351" s="4" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A352" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D352" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="E352" s="4" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A353" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="E353" s="4" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A354" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="E354" s="4" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A355" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="E355" s="4" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A356" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="E356" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A357" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D357" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="E357" s="4" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A358" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="E358" s="4" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A359" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D359" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="E359" s="4" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A360" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="E360" s="4" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A361" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="E361" s="4" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A362" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D362" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="E362" s="4" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A363" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B363" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D363" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="E363" s="4" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A364" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B364" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D364" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="E364" s="4" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A365" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D365" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="E365" s="4" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A366" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B366" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D366" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="E366" s="4" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A367" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="E367" s="4" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A368" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D368" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="E368" s="4" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A369" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="E369" s="4" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A370" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D370" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="E370" s="4" t="s">
+        <v>819</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/backend/data/frameworks/excel/AI Audit Agent - Evaluation Framework.xlsx
+++ b/backend/data/frameworks/excel/AI Audit Agent - Evaluation Framework.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI Audit Platform\backend\data\frameworks\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693FC0D3-9D97-48E1-AC11-34358AFA26EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC3B14A-9F3B-4012-A86E-041F43989357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{397319AA-9A4C-4BE1-B71D-AE2DAE7876CD}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="DEx Evaluation Framework" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DEx Evaluation Framework'!$A$1:$E$369</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STAR Evaluation Framework'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="843">
   <si>
     <t>Document</t>
   </si>
@@ -549,12 +550,6 @@
     <t>Terminology Consistency</t>
   </si>
   <si>
-    <t>Verify whether the same thing is called the same name throughout, with terms defined where they first appear</t>
-  </si>
-  <si>
-    <t>e.g. Refer to HCP as either HCP, doctor, MD, prescriber or physician throughout all the documents.</t>
-  </si>
-  <si>
     <t>Client Repository Sync</t>
   </si>
   <si>
@@ -2574,7 +2569,10 @@
     <t>Verify whether duration, resourcing, discount and estimate all match the executed SOW</t>
   </si>
   <si>
-    <t>Functional Requirement Document (FRD/FSD/FRS)</t>
+    <t>Functional Requirement Document (FRD / FSD / FRS)</t>
+  </si>
+  <si>
+    <t>Verify whether the same thing is called the same name throughout, with terms defined where they first appear e.g. Refer to HCP as either HCP, doctor, MD, prescriber or physician throughout all the documents.</t>
   </si>
 </sst>
 </file>
@@ -2617,7 +2615,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2699,19 +2697,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2724,24 +2709,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2755,22 +2727,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3121,19 +3081,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3496,7 +3456,7 @@
     </row>
     <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>141</v>
@@ -3505,15 +3465,15 @@
         <v>4</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>141</v>
@@ -3522,15 +3482,15 @@
         <v>4</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>141</v>
@@ -3539,15 +3499,15 @@
         <v>4</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>141</v>
@@ -3556,15 +3516,15 @@
         <v>4</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>141</v>
@@ -3573,15 +3533,15 @@
         <v>4</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>141</v>
@@ -3590,15 +3550,15 @@
         <v>4</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>141</v>
@@ -3607,15 +3567,15 @@
         <v>4</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>141</v>
@@ -3624,15 +3584,15 @@
         <v>4</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>141</v>
@@ -3641,15 +3601,15 @@
         <v>4</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>141</v>
@@ -3658,15 +3618,15 @@
         <v>17</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>141</v>
@@ -3675,10 +3635,10 @@
         <v>17</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>
@@ -3688,14 +3648,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B5FC0E-D7D1-4134-97F1-75A2EB32763F}">
-  <dimension ref="A1:E370"/>
+  <dimension ref="A1:E369"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="110.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="146" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -3715,9 +3675,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>139</v>
@@ -3732,9 +3692,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>139</v>
@@ -3749,9 +3709,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>139</v>
@@ -3766,9 +3726,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>139</v>
@@ -3783,9 +3743,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>139</v>
@@ -3800,9 +3760,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>139</v>
@@ -3817,9 +3777,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>139</v>
@@ -3834,9 +3794,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>139</v>
@@ -3851,9 +3811,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>139</v>
@@ -3868,9 +3828,9 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>139</v>
@@ -3885,9 +3845,9 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>139</v>
@@ -3902,9 +3862,9 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>139</v>
@@ -3919,9 +3879,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>139</v>
@@ -3936,9 +3896,9 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>139</v>
@@ -3953,9 +3913,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>139</v>
@@ -3970,9 +3930,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>139</v>
@@ -3987,9 +3947,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>139</v>
@@ -4004,7 +3964,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
@@ -4021,7 +3981,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>26</v>
       </c>
@@ -4038,7 +3998,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>26</v>
       </c>
@@ -4055,7 +4015,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>26</v>
       </c>
@@ -4072,7 +4032,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>26</v>
       </c>
@@ -4089,7 +4049,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -4106,7 +4066,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>26</v>
       </c>
@@ -4123,7 +4083,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
@@ -4140,7 +4100,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
@@ -4191,7 +4151,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>90</v>
       </c>
@@ -4208,7 +4168,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>90</v>
       </c>
@@ -4225,7 +4185,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>90</v>
       </c>
@@ -4242,7 +4202,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>90</v>
       </c>
@@ -4259,7 +4219,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>90</v>
       </c>
@@ -4276,7 +4236,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>90</v>
       </c>
@@ -4293,7 +4253,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>90</v>
       </c>
@@ -4310,7 +4270,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>90</v>
       </c>
@@ -4327,7 +4287,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>90</v>
       </c>
@@ -4344,7 +4304,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>90</v>
       </c>
@@ -4361,7 +4321,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>90</v>
       </c>
@@ -4378,7 +4338,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>90</v>
       </c>
@@ -4395,7 +4355,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>90</v>
       </c>
@@ -4412,7 +4372,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>90</v>
       </c>
@@ -4429,7 +4389,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>90</v>
       </c>
@@ -4446,7 +4406,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>90</v>
       </c>
@@ -4463,7 +4423,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>90</v>
       </c>
@@ -4480,7 +4440,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>90</v>
       </c>
@@ -4497,7 +4457,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>90</v>
       </c>
@@ -4514,7 +4474,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>90</v>
       </c>
@@ -4531,7 +4491,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>90</v>
       </c>
@@ -4548,7 +4508,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>90</v>
       </c>
@@ -4565,7 +4525,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>90</v>
       </c>
@@ -4582,7 +4542,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>157</v>
       </c>
@@ -4599,7 +4559,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>157</v>
       </c>
@@ -4616,7 +4576,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>157</v>
       </c>
@@ -4633,7 +4593,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>157</v>
       </c>
@@ -4650,33 +4610,41 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
+    <row r="57" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" s="9" t="s">
+      <c r="C57" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>167</v>
       </c>
       <c r="E57" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>157</v>
       </c>
@@ -4693,7 +4661,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>157</v>
       </c>
@@ -4710,26 +4678,26 @@
         <v>173</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D61" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>141</v>
@@ -4744,9 +4712,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>141</v>
@@ -4761,9 +4729,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>141</v>
@@ -4778,9 +4746,9 @@
         <v>182</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>141</v>
@@ -4795,9 +4763,9 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>141</v>
@@ -4812,9 +4780,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>141</v>
@@ -4829,9 +4797,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>141</v>
@@ -4846,9 +4814,9 @@
         <v>190</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>141</v>
@@ -4863,9 +4831,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>141</v>
@@ -4880,9 +4848,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>141</v>
@@ -4897,9 +4865,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>141</v>
@@ -4914,9 +4882,9 @@
         <v>198</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>141</v>
@@ -4931,9 +4899,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>141</v>
@@ -4948,9 +4916,9 @@
         <v>202</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>141</v>
@@ -4965,9 +4933,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>141</v>
@@ -4982,9 +4950,9 @@
         <v>206</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>141</v>
@@ -4999,15 +4967,15 @@
         <v>208</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>141</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>209</v>
@@ -5016,9 +4984,9 @@
         <v>210</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>141</v>
@@ -5033,9 +5001,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>141</v>
@@ -5050,29 +5018,29 @@
         <v>214</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>141</v>
+        <v>216</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="B82" s="4" t="s">
         <v>216</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>4</v>
@@ -5084,12 +5052,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>4</v>
@@ -5101,12 +5069,12 @@
         <v>222</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>4</v>
@@ -5118,12 +5086,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>4</v>
@@ -5135,12 +5103,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>4</v>
@@ -5152,12 +5120,12 @@
         <v>228</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>4</v>
@@ -5169,12 +5137,12 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>4</v>
@@ -5186,12 +5154,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>4</v>
@@ -5203,15 +5171,15 @@
         <v>234</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>235</v>
@@ -5220,29 +5188,29 @@
         <v>236</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>4</v>
@@ -5256,10 +5224,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>4</v>
@@ -5273,10 +5241,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>4</v>
@@ -5290,10 +5258,10 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>4</v>
@@ -5307,10 +5275,10 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>4</v>
@@ -5324,10 +5292,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>4</v>
@@ -5341,10 +5309,10 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>4</v>
@@ -5358,10 +5326,10 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>4</v>
@@ -5373,12 +5341,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>4</v>
@@ -5390,12 +5358,12 @@
         <v>257</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>4</v>
@@ -5409,10 +5377,10 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>4</v>
@@ -5426,10 +5394,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>4</v>
@@ -5443,10 +5411,10 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>4</v>
@@ -5460,10 +5428,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>4</v>
@@ -5477,10 +5445,10 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>4</v>
@@ -5494,10 +5462,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>4</v>
@@ -5511,13 +5479,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>272</v>
@@ -5528,33 +5496,33 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D109" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E109" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>191</v>
+        <v>275</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>276</v>
@@ -5562,10 +5530,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>17</v>
@@ -5579,10 +5547,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>17</v>
@@ -5596,10 +5564,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>17</v>
@@ -5613,10 +5581,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>17</v>
@@ -5630,10 +5598,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>17</v>
@@ -5647,10 +5615,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>17</v>
@@ -5664,27 +5632,27 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>239</v>
+        <v>289</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D117" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="E117" s="4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
-        <v>291</v>
-      </c>
       <c r="B118" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>4</v>
@@ -5696,12 +5664,12 @@
         <v>293</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>4</v>
@@ -5713,12 +5681,12 @@
         <v>295</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>4</v>
@@ -5730,12 +5698,12 @@
         <v>297</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>4</v>
@@ -5747,12 +5715,12 @@
         <v>299</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>4</v>
@@ -5764,12 +5732,12 @@
         <v>301</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>4</v>
@@ -5781,29 +5749,29 @@
         <v>303</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>4</v>
@@ -5817,10 +5785,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>4</v>
@@ -5834,10 +5802,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>4</v>
@@ -5851,10 +5819,10 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>4</v>
@@ -5868,10 +5836,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>4</v>
@@ -5885,13 +5853,13 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>317</v>
@@ -5902,10 +5870,10 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>17</v>
@@ -5919,10 +5887,10 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>17</v>
@@ -5936,27 +5904,27 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>4</v>
@@ -5970,10 +5938,10 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>4</v>
@@ -5987,10 +5955,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>4</v>
@@ -6004,10 +5972,10 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>4</v>
@@ -6021,10 +5989,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>4</v>
@@ -6038,10 +6006,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>4</v>
@@ -6055,13 +6023,13 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>338</v>
@@ -6072,10 +6040,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>17</v>
@@ -6089,10 +6057,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>17</v>
@@ -6106,27 +6074,27 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>218</v>
+        <v>345</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D143" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="E143" s="4" t="s">
+      <c r="B144" s="4" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>347</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>4</v>
@@ -6138,12 +6106,12 @@
         <v>349</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>4</v>
@@ -6155,12 +6123,12 @@
         <v>351</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>4</v>
@@ -6172,12 +6140,12 @@
         <v>353</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>4</v>
@@ -6189,12 +6157,12 @@
         <v>355</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>4</v>
@@ -6206,12 +6174,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>4</v>
@@ -6223,12 +6191,12 @@
         <v>359</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>4</v>
@@ -6240,12 +6208,12 @@
         <v>361</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>4</v>
@@ -6257,12 +6225,12 @@
         <v>363</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>4</v>
@@ -6274,12 +6242,12 @@
         <v>365</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>4</v>
@@ -6291,12 +6259,12 @@
         <v>367</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>4</v>
@@ -6308,12 +6276,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>4</v>
@@ -6325,12 +6293,12 @@
         <v>371</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>4</v>
@@ -6342,12 +6310,12 @@
         <v>373</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>4</v>
@@ -6359,12 +6327,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>4</v>
@@ -6376,15 +6344,15 @@
         <v>377</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>378</v>
@@ -6393,12 +6361,12 @@
         <v>379</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>17</v>
@@ -6410,12 +6378,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>17</v>
@@ -6427,12 +6395,12 @@
         <v>383</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>17</v>
@@ -6444,29 +6412,29 @@
         <v>385</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>346</v>
+        <v>386</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D163" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="E163" s="4" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
-        <v>388</v>
-      </c>
       <c r="B164" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>4</v>
@@ -6478,12 +6446,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>4</v>
@@ -6495,12 +6463,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>4</v>
@@ -6512,12 +6480,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>4</v>
@@ -6529,12 +6497,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>4</v>
@@ -6546,12 +6514,12 @@
         <v>398</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>4</v>
@@ -6563,12 +6531,12 @@
         <v>400</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>4</v>
@@ -6580,12 +6548,12 @@
         <v>402</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>4</v>
@@ -6597,12 +6565,12 @@
         <v>404</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>4</v>
@@ -6614,12 +6582,12 @@
         <v>406</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>4</v>
@@ -6631,15 +6599,15 @@
         <v>408</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>409</v>
@@ -6648,12 +6616,12 @@
         <v>410</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>17</v>
@@ -6665,12 +6633,12 @@
         <v>412</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>17</v>
@@ -6682,29 +6650,29 @@
         <v>414</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>347</v>
+        <v>416</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>4</v>
@@ -6718,10 +6686,10 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>4</v>
@@ -6735,10 +6703,10 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>4</v>
@@ -6752,10 +6720,10 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>4</v>
@@ -6769,10 +6737,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>4</v>
@@ -6786,10 +6754,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>4</v>
@@ -6803,10 +6771,10 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>4</v>
@@ -6820,10 +6788,10 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>4</v>
@@ -6837,13 +6805,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>435</v>
@@ -6854,10 +6822,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>17</v>
@@ -6871,10 +6839,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>17</v>
@@ -6888,10 +6856,10 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>17</v>
@@ -6905,24 +6873,24 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>418</v>
+        <v>158</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D190" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="E190" s="4" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A191" s="3" t="s">
-        <v>445</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>158</v>
@@ -6937,9 +6905,9 @@
         <v>447</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>158</v>
@@ -6954,9 +6922,9 @@
         <v>449</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>158</v>
@@ -6971,9 +6939,9 @@
         <v>451</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>158</v>
@@ -6988,9 +6956,9 @@
         <v>453</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>158</v>
@@ -7005,9 +6973,9 @@
         <v>455</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>158</v>
@@ -7022,9 +6990,9 @@
         <v>457</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>158</v>
@@ -7039,9 +7007,9 @@
         <v>459</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>158</v>
@@ -7056,9 +7024,9 @@
         <v>461</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>158</v>
@@ -7073,9 +7041,9 @@
         <v>463</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>158</v>
@@ -7090,15 +7058,15 @@
         <v>465</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>158</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>466</v>
@@ -7107,9 +7075,9 @@
         <v>467</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>158</v>
@@ -7124,9 +7092,9 @@
         <v>469</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>158</v>
@@ -7141,29 +7109,29 @@
         <v>471</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>4</v>
@@ -7177,10 +7145,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>4</v>
@@ -7194,10 +7162,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>4</v>
@@ -7211,10 +7179,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>4</v>
@@ -7228,10 +7196,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>4</v>
@@ -7245,10 +7213,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>4</v>
@@ -7262,13 +7230,13 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>487</v>
@@ -7279,10 +7247,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>17</v>
@@ -7296,10 +7264,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>17</v>
@@ -7313,24 +7281,24 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>218</v>
+        <v>139</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D214" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E214" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A215" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="E214" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A215" s="3" t="s">
-        <v>495</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>139</v>
@@ -7345,9 +7313,9 @@
         <v>497</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>139</v>
@@ -7362,9 +7330,9 @@
         <v>499</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>139</v>
@@ -7379,9 +7347,9 @@
         <v>501</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>139</v>
@@ -7396,9 +7364,9 @@
         <v>503</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>139</v>
@@ -7413,9 +7381,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>139</v>
@@ -7430,9 +7398,9 @@
         <v>507</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>139</v>
@@ -7447,9 +7415,9 @@
         <v>509</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B222" s="4" t="s">
         <v>139</v>
@@ -7464,9 +7432,9 @@
         <v>511</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>139</v>
@@ -7481,15 +7449,15 @@
         <v>513</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>139</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D224" s="4" t="s">
         <v>514</v>
@@ -7498,9 +7466,9 @@
         <v>515</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>139</v>
@@ -7515,29 +7483,29 @@
         <v>517</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>139</v>
+        <v>519</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D226" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="E226" s="4" t="s">
+      <c r="B227" s="4" t="s">
         <v>519</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A227" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>521</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>4</v>
@@ -7549,12 +7517,12 @@
         <v>523</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>4</v>
@@ -7566,12 +7534,12 @@
         <v>525</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>4</v>
@@ -7583,12 +7551,12 @@
         <v>527</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>4</v>
@@ -7600,12 +7568,12 @@
         <v>529</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>4</v>
@@ -7617,12 +7585,12 @@
         <v>531</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>4</v>
@@ -7634,12 +7602,12 @@
         <v>533</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>4</v>
@@ -7651,12 +7619,12 @@
         <v>535</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>4</v>
@@ -7668,12 +7636,12 @@
         <v>537</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>4</v>
@@ -7685,12 +7653,12 @@
         <v>539</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>4</v>
@@ -7702,12 +7670,12 @@
         <v>541</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>4</v>
@@ -7719,12 +7687,12 @@
         <v>543</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>4</v>
@@ -7736,12 +7704,12 @@
         <v>545</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>4</v>
@@ -7753,12 +7721,12 @@
         <v>547</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>4</v>
@@ -7770,12 +7738,12 @@
         <v>549</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>4</v>
@@ -7787,12 +7755,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>4</v>
@@ -7804,12 +7772,12 @@
         <v>553</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>4</v>
@@ -7821,12 +7789,12 @@
         <v>555</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>4</v>
@@ -7838,12 +7806,12 @@
         <v>557</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>4</v>
@@ -7855,12 +7823,12 @@
         <v>559</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>4</v>
@@ -7872,12 +7840,12 @@
         <v>561</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>4</v>
@@ -7889,12 +7857,12 @@
         <v>563</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>4</v>
@@ -7906,12 +7874,12 @@
         <v>565</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>4</v>
@@ -7923,12 +7891,12 @@
         <v>567</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>4</v>
@@ -7940,15 +7908,15 @@
         <v>569</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D251" s="4" t="s">
         <v>570</v>
@@ -7957,12 +7925,12 @@
         <v>571</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>17</v>
@@ -7974,12 +7942,12 @@
         <v>573</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>17</v>
@@ -7991,12 +7959,12 @@
         <v>575</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>17</v>
@@ -8008,12 +7976,12 @@
         <v>577</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>17</v>
@@ -8025,12 +7993,12 @@
         <v>579</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>17</v>
@@ -8042,12 +8010,12 @@
         <v>581</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>17</v>
@@ -8059,29 +8027,29 @@
         <v>583</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
-        <v>520</v>
+        <v>584</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E258" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>4</v>
@@ -8095,10 +8063,10 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>4</v>
@@ -8112,10 +8080,10 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>4</v>
@@ -8129,10 +8097,10 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>4</v>
@@ -8146,10 +8114,10 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>4</v>
@@ -8163,10 +8131,10 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>4</v>
@@ -8180,10 +8148,10 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>4</v>
@@ -8197,10 +8165,10 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>4</v>
@@ -8214,13 +8182,13 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>603</v>
@@ -8231,10 +8199,10 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>17</v>
@@ -8248,27 +8216,27 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E269" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>4</v>
@@ -8282,10 +8250,10 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>4</v>
@@ -8299,10 +8267,10 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>4</v>
@@ -8316,10 +8284,10 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>4</v>
@@ -8333,10 +8301,10 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>4</v>
@@ -8350,13 +8318,13 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>620</v>
@@ -8367,10 +8335,10 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>17</v>
@@ -8384,27 +8352,27 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D277" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="E277" s="4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A278" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="E277" s="4" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A278" s="3" t="s">
-        <v>626</v>
-      </c>
       <c r="B278" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C278" s="4" t="s">
         <v>4</v>
@@ -8416,12 +8384,12 @@
         <v>628</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C279" s="4" t="s">
         <v>4</v>
@@ -8433,12 +8401,12 @@
         <v>630</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C280" s="4" t="s">
         <v>4</v>
@@ -8450,12 +8418,12 @@
         <v>632</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C281" s="4" t="s">
         <v>4</v>
@@ -8467,12 +8435,12 @@
         <v>634</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>4</v>
@@ -8484,12 +8452,12 @@
         <v>636</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>4</v>
@@ -8501,15 +8469,15 @@
         <v>638</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>639</v>
@@ -8518,12 +8486,12 @@
         <v>640</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>17</v>
@@ -8535,12 +8503,12 @@
         <v>642</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>17</v>
@@ -8552,12 +8520,12 @@
         <v>644</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>17</v>
@@ -8569,29 +8537,29 @@
         <v>646</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D288" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="E288" s="4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A289" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="E288" s="4" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A289" s="3" t="s">
-        <v>649</v>
-      </c>
       <c r="B289" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>4</v>
@@ -8603,12 +8571,12 @@
         <v>651</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>4</v>
@@ -8620,12 +8588,12 @@
         <v>653</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C291" s="4" t="s">
         <v>4</v>
@@ -8637,12 +8605,12 @@
         <v>655</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>4</v>
@@ -8654,12 +8622,12 @@
         <v>657</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>4</v>
@@ -8671,12 +8639,12 @@
         <v>659</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>4</v>
@@ -8688,12 +8656,12 @@
         <v>661</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>4</v>
@@ -8705,15 +8673,15 @@
         <v>663</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>664</v>
@@ -8722,12 +8690,12 @@
         <v>665</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>17</v>
@@ -8739,29 +8707,29 @@
         <v>667</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>521</v>
+        <v>669</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E298" s="4" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>4</v>
@@ -8775,10 +8743,10 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>4</v>
@@ -8792,10 +8760,10 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>4</v>
@@ -8809,10 +8777,10 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>4</v>
@@ -8826,10 +8794,10 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>4</v>
@@ -8843,10 +8811,10 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>4</v>
@@ -8860,10 +8828,10 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>4</v>
@@ -8877,10 +8845,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>4</v>
@@ -8894,13 +8862,13 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>688</v>
@@ -8911,10 +8879,10 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>17</v>
@@ -8928,10 +8896,10 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>17</v>
@@ -8945,24 +8913,24 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
-        <v>670</v>
+        <v>694</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>671</v>
+        <v>140</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D310" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A311" s="3" t="s">
         <v>694</v>
-      </c>
-      <c r="E310" s="4" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A311" s="3" t="s">
-        <v>696</v>
       </c>
       <c r="B311" s="4" t="s">
         <v>140</v>
@@ -8977,9 +8945,9 @@
         <v>698</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B312" s="4" t="s">
         <v>140</v>
@@ -8994,9 +8962,9 @@
         <v>700</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B313" s="4" t="s">
         <v>140</v>
@@ -9011,9 +8979,9 @@
         <v>702</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B314" s="4" t="s">
         <v>140</v>
@@ -9028,9 +8996,9 @@
         <v>704</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B315" s="4" t="s">
         <v>140</v>
@@ -9045,9 +9013,9 @@
         <v>706</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B316" s="4" t="s">
         <v>140</v>
@@ -9062,9 +9030,9 @@
         <v>708</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B317" s="4" t="s">
         <v>140</v>
@@ -9079,15 +9047,15 @@
         <v>710</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B318" s="4" t="s">
         <v>140</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>711</v>
@@ -9096,9 +9064,9 @@
         <v>712</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B319" s="4" t="s">
         <v>140</v>
@@ -9113,9 +9081,9 @@
         <v>714</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B320" s="4" t="s">
         <v>140</v>
@@ -9130,9 +9098,9 @@
         <v>716</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B321" s="4" t="s">
         <v>140</v>
@@ -9147,29 +9115,29 @@
         <v>718</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
-        <v>696</v>
+        <v>719</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>140</v>
+        <v>720</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D322" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="E322" s="4" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A323" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="E322" s="4" t="s">
+      <c r="B323" s="4" t="s">
         <v>720</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A323" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="B323" s="4" t="s">
-        <v>722</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>4</v>
@@ -9181,12 +9149,12 @@
         <v>724</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>4</v>
@@ -9198,12 +9166,12 @@
         <v>726</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>4</v>
@@ -9215,12 +9183,12 @@
         <v>728</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>4</v>
@@ -9232,12 +9200,12 @@
         <v>730</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>4</v>
@@ -9249,12 +9217,12 @@
         <v>732</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>4</v>
@@ -9266,49 +9234,49 @@
         <v>734</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D329" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="E329" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="E329" s="4" t="s">
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A330" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D330" s="4" t="s">
         <v>736</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A330" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="B330" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="C330" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D330" s="4" t="s">
-        <v>686</v>
       </c>
       <c r="E330" s="4" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>738</v>
@@ -9317,12 +9285,12 @@
         <v>739</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>17</v>
@@ -9334,29 +9302,29 @@
         <v>741</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E333" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>4</v>
@@ -9370,10 +9338,10 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>4</v>
@@ -9387,10 +9355,10 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>4</v>
@@ -9404,10 +9372,10 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>4</v>
@@ -9421,10 +9389,10 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>4</v>
@@ -9438,10 +9406,10 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>4</v>
@@ -9455,10 +9423,10 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>4</v>
@@ -9472,10 +9440,10 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>4</v>
@@ -9489,10 +9457,10 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>4</v>
@@ -9506,10 +9474,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>4</v>
@@ -9523,10 +9491,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>4</v>
@@ -9540,10 +9508,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>4</v>
@@ -9557,13 +9525,13 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>769</v>
@@ -9574,10 +9542,10 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>17</v>
@@ -9591,10 +9559,10 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>17</v>
@@ -9608,10 +9576,10 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>17</v>
@@ -9625,24 +9593,24 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
-        <v>744</v>
+        <v>777</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>722</v>
+        <v>158</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D350" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="E350" s="4" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A351" s="3" t="s">
         <v>777</v>
-      </c>
-      <c r="E350" s="4" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A351" s="3" t="s">
-        <v>779</v>
       </c>
       <c r="B351" s="4" t="s">
         <v>158</v>
@@ -9657,9 +9625,9 @@
         <v>781</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B352" s="4" t="s">
         <v>158</v>
@@ -9674,9 +9642,9 @@
         <v>783</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B353" s="4" t="s">
         <v>158</v>
@@ -9691,9 +9659,9 @@
         <v>785</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B354" s="4" t="s">
         <v>158</v>
@@ -9708,9 +9676,9 @@
         <v>787</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B355" s="4" t="s">
         <v>158</v>
@@ -9725,9 +9693,9 @@
         <v>789</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B356" s="4" t="s">
         <v>158</v>
@@ -9742,9 +9710,9 @@
         <v>791</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B357" s="4" t="s">
         <v>158</v>
@@ -9759,9 +9727,9 @@
         <v>793</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B358" s="4" t="s">
         <v>158</v>
@@ -9776,9 +9744,9 @@
         <v>795</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B359" s="4" t="s">
         <v>158</v>
@@ -9793,9 +9761,9 @@
         <v>797</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B360" s="4" t="s">
         <v>158</v>
@@ -9810,9 +9778,9 @@
         <v>799</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B361" s="4" t="s">
         <v>158</v>
@@ -9827,9 +9795,9 @@
         <v>801</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B362" s="4" t="s">
         <v>158</v>
@@ -9844,9 +9812,9 @@
         <v>803</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B363" s="4" t="s">
         <v>158</v>
@@ -9861,15 +9829,15 @@
         <v>805</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B364" s="4" t="s">
         <v>158</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>806</v>
@@ -9878,9 +9846,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B365" s="4" t="s">
         <v>158</v>
@@ -9895,9 +9863,9 @@
         <v>809</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B366" s="4" t="s">
         <v>158</v>
@@ -9912,9 +9880,9 @@
         <v>811</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B367" s="4" t="s">
         <v>158</v>
@@ -9929,9 +9897,9 @@
         <v>813</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B368" s="4" t="s">
         <v>158</v>
@@ -9946,9 +9914,9 @@
         <v>815</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B369" s="4" t="s">
         <v>158</v>
@@ -9963,30 +9931,8 @@
         <v>817</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A370" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="B370" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C370" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D370" s="4" t="s">
-        <v>818</v>
-      </c>
-      <c r="E370" s="4" t="s">
-        <v>819</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-  </mergeCells>
+  <autoFilter ref="A1:E369" xr:uid="{38B5FC0E-D7D1-4134-97F1-75A2EB32763F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
